--- a/data/trans_dic/P57_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Estudios-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,97; 33,59</t>
+          <t>27,31; 33,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,85; 33,06</t>
+          <t>25,56; 32,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,78; 42,01</t>
+          <t>35,73; 42,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 39,11</t>
+          <t>33,84; 39,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,78; 37,58</t>
+          <t>32,76; 37,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,42; 35,58</t>
+          <t>31,03; 35,49</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 17,92</t>
+          <t>14,57; 17,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,36</t>
+          <t>6,8; 11,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 21,39</t>
+          <t>18,01; 21,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,91</t>
+          <t>8,07; 12,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,67; 19,06</t>
+          <t>16,54; 19,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,76</t>
+          <t>8,27; 11,72</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,49</t>
+          <t>8,41; 14,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,26</t>
+          <t>6,75; 11,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,7</t>
+          <t>6,99; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,17</t>
+          <t>6,59; 10,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,27</t>
+          <t>8,39; 12,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,01</t>
+          <t>7,34; 10,17</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,84</t>
+          <t>17,14; 19,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,9</t>
+          <t>9,64; 13,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,88; 24,78</t>
+          <t>21,91; 24,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 17,23</t>
+          <t>12,96; 17,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 22,11</t>
+          <t>19,99; 21,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,21</t>
+          <t>12,14; 15,23</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>202909; 252653</t>
+          <t>205465; 254817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131139; 167716</t>
+          <t>129669; 166965</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>354566; 416353</t>
+          <t>354107; 418380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252543; 290687</t>
+          <t>251487; 291650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>571381; 655066</t>
+          <t>571054; 655249</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>392920; 444890</t>
+          <t>388043; 443808</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>299821; 370463</t>
+          <t>301237; 368541</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152459; 259949</t>
+          <t>155615; 265314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>351268; 423256</t>
+          <t>356384; 425936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180185; 287943</t>
+          <t>180102; 286706</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>674329; 770985</t>
+          <t>669153; 770544</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>381681; 531592</t>
+          <t>373569; 529882</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47520; 78975</t>
+          <t>45856; 76352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42257; 72750</t>
+          <t>43586; 73055</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35848; 63853</t>
+          <t>38147; 65529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43116; 66939</t>
+          <t>43396; 68302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92640; 133882</t>
+          <t>91473; 131902</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93872; 130621</t>
+          <t>95756; 132601</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>579798; 667515</t>
+          <t>576623; 666498</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>332307; 478277</t>
+          <t>331848; 479589</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>769112; 871063</t>
+          <t>770165; 873325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>463279; 626063</t>
+          <t>470926; 624131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1378317; 1520852</t>
+          <t>1375106; 1512121</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>841638; 1076191</t>
+          <t>858581; 1077260</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,31; 33,87</t>
+          <t>27,06; 33,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,56; 32,91</t>
+          <t>25,05; 31,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,73; 42,22</t>
+          <t>35,66; 42,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,84; 39,24</t>
+          <t>34,15; 39,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,76; 37,59</t>
+          <t>32,98; 37,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,03; 35,49</t>
+          <t>30,97; 35,05</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 17,83</t>
+          <t>14,54; 17,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,59</t>
+          <t>9,65; 12,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 21,53</t>
+          <t>17,96; 21,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,85</t>
+          <t>11,79; 14,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 19,05</t>
+          <t>16,62; 19,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,72</t>
+          <t>11,16; 12,97</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,01</t>
+          <t>8,63; 14,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,31</t>
+          <t>6,77; 11,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,0</t>
+          <t>6,6; 12,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,37</t>
+          <t>6,71; 10,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,09</t>
+          <t>8,4; 12,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,17</t>
+          <t>7,23; 10,13</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 19,81</t>
+          <t>17,33; 19,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,93</t>
+          <t>12,26; 14,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,91; 24,84</t>
+          <t>21,92; 24,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 17,18</t>
+          <t>16,2; 18,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,99; 21,98</t>
+          <t>19,88; 21,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,23</t>
+          <t>14,55; 16,1</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>148042</t>
+          <t>161295</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269794</t>
+          <t>296031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>417836</t>
+          <t>457326</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>205465; 254817</t>
+          <t>203524; 253584</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>129669; 166965</t>
+          <t>142875; 181530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>354107; 418380</t>
+          <t>353375; 418511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251487; 291650</t>
+          <t>276454; 317276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>571054; 655249</t>
+          <t>574935; 655810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>388043; 443808</t>
+          <t>427273; 483678</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>223482</t>
+          <t>245396</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245496</t>
+          <t>282397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>468977</t>
+          <t>527793</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>301237; 368541</t>
+          <t>300575; 369542</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>155615; 265314</t>
+          <t>215099; 276090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>356384; 425936</t>
+          <t>355326; 425213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>180102; 286706</t>
+          <t>255095; 309998</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>669153; 770544</t>
+          <t>672278; 780266</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>373569; 529882</t>
+          <t>490279; 569914</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>63823</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>61565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>111782</t>
+          <t>125389</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45856; 76352</t>
+          <t>47008; 77800</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43586; 73055</t>
+          <t>48117; 83199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38147; 65529</t>
+          <t>36026; 66582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43396; 68302</t>
+          <t>49188; 75808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91473; 131902</t>
+          <t>91579; 134221</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95756; 132601</t>
+          <t>104387; 146237</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>428692</t>
+          <t>470513</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>569903</t>
+          <t>639994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>998594</t>
+          <t>1110507</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>576623; 666498</t>
+          <t>583062; 672207</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>331848; 479589</t>
+          <t>430247; 514082</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>770165; 873325</t>
+          <t>770799; 874597</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>470926; 624131</t>
+          <t>600302; 676521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1375106; 1512121</t>
+          <t>1367921; 1512895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>858581; 1077260</t>
+          <t>1050032; 1161955</t>
         </is>
       </c>
     </row>
